--- a/data/gravel/Quirk SUPERCHUB 2025.xlsx
+++ b/data/gravel/Quirk SUPERCHUB 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5ED9DD-B084-6749-A2AE-68BF1248EE27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EC1DDD7-EFAB-D149-81A5-FBAC88946A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2720" yWindow="520" windowWidth="26080" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1204,13 +1204,13 @@
       <c r="A42" t="s">
         <v>35</v>
       </c>
-      <c r="B42">
-        <v>100</v>
-      </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>36</v>
+      </c>
+      <c r="B43">
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">

--- a/data/gravel/Quirk SUPERCHUB 2025.xlsx
+++ b/data/gravel/Quirk SUPERCHUB 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EC1DDD7-EFAB-D149-81A5-FBAC88946A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD893488-7C1E-B041-9B25-340879553EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2720" yWindow="520" windowWidth="26080" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="103">
   <si>
     <t>brand</t>
   </si>
@@ -336,6 +336,12 @@
   </si>
   <si>
     <t>suspension</t>
+  </si>
+  <si>
+    <t>geom based on rigid fork. Must be 100 mm so this should be 503. Estimate is 498</t>
+  </si>
+  <si>
+    <t>https://images.squarespace-cdn.com/content/v1/55ec22b7e4b08b68bec3a4f6/1636477347117-5FXYFODP42Q5JRS8DNKG/Quirk_Cycles_SUPERCHUB_01.jpg?format=1500w</t>
   </si>
 </sst>
 </file>
@@ -735,6 +741,11 @@
         <v>93</v>
       </c>
     </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>102</v>
+      </c>
+    </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
@@ -1037,6 +1048,21 @@
       <c r="A22" t="s">
         <v>21</v>
       </c>
+      <c r="C22" s="2">
+        <v>503</v>
+      </c>
+      <c r="D22" s="2">
+        <v>503</v>
+      </c>
+      <c r="E22" s="2">
+        <v>503</v>
+      </c>
+      <c r="F22" s="2">
+        <v>503</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>101</v>
+      </c>
       <c r="I22" s="2"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">

--- a/data/gravel/Quirk SUPERCHUB 2025.xlsx
+++ b/data/gravel/Quirk SUPERCHUB 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD893488-7C1E-B041-9B25-340879553EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C857CC3-A478-FF46-AF27-329B08C2A506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2720" yWindow="520" windowWidth="26080" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="105">
   <si>
     <t>brand</t>
   </si>
@@ -342,6 +342,12 @@
   </si>
   <si>
     <t>https://images.squarespace-cdn.com/content/v1/55ec22b7e4b08b68bec3a4f6/1636477347117-5FXYFODP42Q5JRS8DNKG/Quirk_Cycles_SUPERCHUB_01.jpg?format=1500w</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>East London, UK</t>
   </si>
 </sst>
 </file>
@@ -695,7 +701,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1422,6 +1428,14 @@
         <v>89</v>
       </c>
     </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>103</v>
+      </c>
+      <c r="B73" t="s">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Quirk SUPERCHUB 2025.xlsx
+++ b/data/gravel/Quirk SUPERCHUB 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C857CC3-A478-FF46-AF27-329B08C2A506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53049FBF-CAB6-8A4C-AF60-E9BAA949899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2720" yWindow="520" windowWidth="26080" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="111">
   <si>
     <t>brand</t>
   </si>
@@ -348,6 +348,24 @@
   </si>
   <si>
     <t>East London, UK</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -701,7 +719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1278,161 +1296,191 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>43</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51">
-        <v>31.6</v>
+        <v>107</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="2"/>
+        <v>108</v>
+      </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>46</v>
+        <v>109</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>110</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>49</v>
-      </c>
-      <c r="B56">
-        <v>180</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B57">
+        <v>31.6</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>51</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>95</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B58" s="2"/>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>52</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>98</v>
+        <v>46</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>53</v>
-      </c>
-      <c r="B60" s="2"/>
+        <v>47</v>
+      </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>55</v>
+        <v>49</v>
+      </c>
+      <c r="B62">
+        <v>180</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>57</v>
-      </c>
-      <c r="B64" s="2"/>
+        <v>51</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>58</v>
+        <v>52</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B66" s="2"/>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>60</v>
-      </c>
-      <c r="B67" s="2"/>
+        <v>54</v>
+      </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>61</v>
-      </c>
-      <c r="B68" s="2"/>
+        <v>55</v>
+      </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>62</v>
-      </c>
-      <c r="B69">
-        <v>4200</v>
-      </c>
-      <c r="C69" s="2"/>
+        <v>56</v>
+      </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>63</v>
-      </c>
-      <c r="B70">
-        <v>7000</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B70" s="2"/>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>64</v>
-      </c>
-      <c r="B71" s="2"/>
+        <v>58</v>
+      </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>65</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>89</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B72" s="2"/>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>60</v>
+      </c>
+      <c r="B73" s="2"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>61</v>
+      </c>
+      <c r="B74" s="2"/>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>62</v>
+      </c>
+      <c r="B75">
+        <v>4200</v>
+      </c>
+      <c r="C75" s="2"/>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>63</v>
+      </c>
+      <c r="B76">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>64</v>
+      </c>
+      <c r="B77" s="2"/>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>103</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>104</v>
       </c>
     </row>

--- a/data/gravel/Quirk SUPERCHUB 2025.xlsx
+++ b/data/gravel/Quirk SUPERCHUB 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53049FBF-CAB6-8A4C-AF60-E9BAA949899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CCCD354-AF83-3644-908A-FF86609A855D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2720" yWindow="520" windowWidth="26080" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="114">
   <si>
     <t>brand</t>
   </si>
@@ -251,9 +251,6 @@
     <t>flat bar</t>
   </si>
   <si>
-    <t>a8:f32</t>
-  </si>
-  <si>
     <t>Quirk</t>
   </si>
   <si>
@@ -366,6 +363,18 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>100-120</t>
+  </si>
+  <si>
+    <t>a8:f34</t>
   </si>
 </sst>
 </file>
@@ -719,7 +728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -730,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -738,7 +747,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -762,12 +771,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -775,7 +784,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>72</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="22" x14ac:dyDescent="0.3">
@@ -783,16 +792,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" t="s">
         <v>74</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>75</v>
-      </c>
-      <c r="E8" t="s">
-        <v>76</v>
       </c>
       <c r="F8" t="s">
         <v>69</v>
@@ -808,7 +817,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C9">
         <v>607</v>
@@ -829,7 +838,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C10">
         <v>400</v>
@@ -850,7 +859,7 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C11">
         <v>74</v>
@@ -871,7 +880,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C12">
         <v>68</v>
@@ -892,7 +901,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C13">
         <v>433</v>
@@ -913,7 +922,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C14">
         <v>60</v>
@@ -938,7 +947,7 @@
         <v>70</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C15">
         <v>102</v>
@@ -958,7 +967,7 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C16">
         <v>400</v>
@@ -979,7 +988,7 @@
         <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C17">
         <v>100</v>
@@ -1000,7 +1009,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C18">
         <v>569</v>
@@ -1021,7 +1030,7 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C19">
         <v>1097</v>
@@ -1042,7 +1051,7 @@
         <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C20">
         <v>44</v>
@@ -1085,153 +1094,167 @@
         <v>503</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I22" s="2"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" s="2">
+        <v>100</v>
+      </c>
+      <c r="D23" s="2">
+        <v>100</v>
+      </c>
+      <c r="E23" s="2">
+        <v>100</v>
+      </c>
+      <c r="F23" s="2">
+        <v>100</v>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="I23" s="2"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="I24" s="2"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>23</v>
-      </c>
-      <c r="E24">
-        <v>1900</v>
-      </c>
-      <c r="I24" s="2"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>18</v>
-      </c>
-      <c r="I25" s="2"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="E26">
+        <v>1900</v>
       </c>
       <c r="I26" s="2"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I27" s="2"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28">
-        <v>700</v>
-      </c>
-      <c r="D28">
-        <v>700</v>
-      </c>
-      <c r="E28">
-        <v>700</v>
-      </c>
-      <c r="F28">
-        <v>700</v>
+        <v>20</v>
       </c>
       <c r="I28" s="2"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>25</v>
-      </c>
-      <c r="C29">
-        <v>2.4</v>
-      </c>
-      <c r="D29">
-        <v>2.4</v>
-      </c>
-      <c r="E29">
-        <v>2.4</v>
-      </c>
-      <c r="F29">
-        <v>2.4</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H29" s="2"/>
+        <v>19</v>
+      </c>
       <c r="I29" s="2"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C30">
-        <v>2.4</v>
+        <v>700</v>
       </c>
       <c r="D30">
-        <v>2.4</v>
+        <v>700</v>
       </c>
       <c r="E30">
-        <v>2.4</v>
+        <v>700</v>
       </c>
       <c r="F30">
-        <v>2.4</v>
+        <v>700</v>
       </c>
       <c r="I30" s="2"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C31">
+        <v>2.4</v>
+      </c>
+      <c r="D31">
+        <v>2.4</v>
+      </c>
+      <c r="E31">
+        <v>2.4</v>
+      </c>
+      <c r="F31">
+        <v>2.4</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>26</v>
+      </c>
+      <c r="C32">
+        <v>2.4</v>
+      </c>
+      <c r="D32">
+        <v>2.4</v>
+      </c>
+      <c r="E32">
+        <v>2.4</v>
+      </c>
+      <c r="F32">
+        <v>2.4</v>
+      </c>
+      <c r="I32" s="2"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>29</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>66</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>99</v>
@@ -1239,249 +1262,268 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>34</v>
-      </c>
-      <c r="B41">
-        <v>2.4</v>
+        <v>32</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B43">
-        <v>100</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>39</v>
+        <v>37</v>
+      </c>
+      <c r="B46">
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="2">
-        <v>148</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48">
-        <v>110</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>105</v>
+        <v>40</v>
+      </c>
+      <c r="B49" s="2">
+        <v>148</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>106</v>
+        <v>41</v>
+      </c>
+      <c r="B50">
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>42</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>44</v>
-      </c>
-      <c r="B57">
-        <v>31.6</v>
+        <v>42</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>45</v>
-      </c>
-      <c r="B58" s="2"/>
+        <v>43</v>
+      </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>46</v>
+        <v>44</v>
+      </c>
+      <c r="B59">
+        <v>31.6</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>47</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B60" s="2"/>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>49</v>
-      </c>
-      <c r="B62">
-        <v>180</v>
+        <v>47</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>51</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>95</v>
+        <v>49</v>
+      </c>
+      <c r="B64">
+        <v>180</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>52</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>53</v>
-      </c>
-      <c r="B66" s="2"/>
+        <v>51</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>54</v>
+        <v>52</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>55</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B68" s="2"/>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>57</v>
-      </c>
-      <c r="B70" s="2"/>
+        <v>55</v>
+      </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B72" s="2"/>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>60</v>
-      </c>
-      <c r="B73" s="2"/>
+        <v>58</v>
+      </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B74" s="2"/>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>62</v>
-      </c>
-      <c r="B75">
-        <v>4200</v>
-      </c>
-      <c r="C75" s="2"/>
+        <v>60</v>
+      </c>
+      <c r="B75" s="2"/>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>63</v>
-      </c>
-      <c r="B76">
-        <v>7000</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="B76" s="2"/>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>64</v>
-      </c>
-      <c r="B77" s="2"/>
+        <v>62</v>
+      </c>
+      <c r="B77">
+        <v>4200</v>
+      </c>
+      <c r="C77" s="2"/>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>65</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>89</v>
+        <v>63</v>
+      </c>
+      <c r="B78">
+        <v>7000</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
+        <v>64</v>
+      </c>
+      <c r="B79" s="2"/>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>65</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>102</v>
+      </c>
+      <c r="B81" t="s">
         <v>103</v>
-      </c>
-      <c r="B79" t="s">
-        <v>104</v>
       </c>
     </row>
   </sheetData>
